--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationtiming.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationtiming.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationtiming.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationtiming.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -654,7 +654,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/timing-abbreviation</t>
+    <t>http://hl7.org/fhir/ValueSet/timing-abbreviation|4.3.0</t>
   </si>
   <si>
     <t>QSC.code</t>
@@ -964,17 +964,17 @@
   <dimension ref="A1:AL25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.5" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="27.5" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="21.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="23.578125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="23.578125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="17.24609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="14.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -983,24 +983,24 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="44.3046875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="42.51171875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="28.1484375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationtiming.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationtiming.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationtiming.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationtiming.xlsx
@@ -259,11 +259,12 @@
     <t>投与日時</t>
   </si>
   <si>
-    <t>Describes the occurrence of an event that may occur multiple times. Timing schedules are used for specifying when events are expected or requested to occur, and may also be used to represent the summary of a past or ongoing event.  For simplicity, the definitions of Timing components are expressed as 'future' events, but such components can also be used to describe historic or ongoing events.
+    <t>複数回発生する可能性のあるイベントの発生について説明します。タイミングスケジュールは、イベントが発生することが予想または要求される時期を指定するために使用され、過去または進行中のイベントの概要を表すためにも使用できます。簡単にするために、タイミングコンポーネントの定義は「将来の」イベントとして表現されますが、そのようなコンポーネントは歴史的または進行中のイベントを説明するためにも使用できます。
+タイミングスケジュールは、イベントが発生したときのイベントおよび/または基準のリストであり、構造化された形式またはコードとして表現できます。イベントと繰り返し仕様の両方が提供される場合、イベントのリストは、繰り返し構造の情報の解釈として理解されるべきです。 / Describes the occurrence of an event that may occur multiple times. Timing schedules are used for specifying when events are expected or requested to occur, and may also be used to represent the summary of a past or ongoing event.  For simplicity, the definitions of Timing components are expressed as 'future' events, but such components can also be used to describe historic or ongoing events.
 A Timing schedule can be a list of events and/or criteria for when the event happens, which can be expressed in a structured form and/or as a code. When both event and a repeating specification are provided, the list of events should be understood as an interpretation of the information in the repeat structure.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -283,10 +284,10 @@
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -306,13 +307,13 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -328,8 +329,8 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Timing.modifierExtension</t>
@@ -342,14 +343,15 @@
     <t>Y</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -368,7 +370,7 @@
     <t>服用タイミングを具体的な日時で指定する場合に使用する</t>
   </si>
   <si>
-    <t>In a Medication Administration Record, for instance, you need to take a general specification, and turn it into a precise specification.</t>
+    <t>たとえば、投薬投与の記録では、一般的な仕様を取得し、それを正確な仕様に変える必要があります。 / In a Medication Administration Record, for instance, you need to take a general specification, and turn it into a precise specification.</t>
   </si>
   <si>
     <t>QLIST&lt;TS&gt;</t>
@@ -390,8 +392,8 @@
     <t>スケジュールされたタイミングの多くは規則的な繰り返しで決定されている。</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-tim-1:if there's a duration, there needs to be duration units {duration.empty() or durationUnit.exists()}tim-2:if there's a period, there needs to be period units {period.empty() or periodUnit.exists()}tim-4:duration SHALL be a non-negative value {duration.exists() implies duration &gt;= 0}tim-5:period SHALL be a non-negative value {period.exists() implies period &gt;= 0}tim-6:If there's a periodMax, there must be a period {periodMax.empty() or period.exists()}tim-7:If there's a durationMax, there must be a duration {durationMax.empty() or duration.exists()}tim-8:If there's a countMax, there must be a count {countMax.empty() or count.exists()}tim-9:If there's an offset, there must be a when (and not C, CM, CD, CV) {offset.empty() or (when.exists() and ((when in ('C' | 'CM' | 'CD' | 'CV')).not()))}tim-10:If there's a timeOfDay, there cannot be a when, or vice versa {timeOfDay.empty() or when.empty()}</t>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+tim-1:期間がある場合は、期間単位が必要です / if there's a duration, there needs to be duration units {duration.empty() or durationUnit.exists()}tim-2:期間がある場合、期間単位が必要です / if there's a period, there needs to be period units {period.empty() or periodUnit.exists()}tim-4:期間は非陰性価値です / duration SHALL be a non-negative value {duration.exists() implies duration &gt;= 0}tim-5:期間は非陰性の価値です / period SHALL be a non-negative value {period.exists() implies period &gt;= 0}tim-6:期間がある場合、期間がなければなりません / If there's a periodMax, there must be a period {periodMax.empty() or period.exists()}tim-7:Hurtermaxがある場合、期間がなければなりません / If there's a durationMax, there must be a duration {durationMax.empty() or duration.exists()}tim-8:countmaxがある場合、カウントが必要です / If there's a countMax, there must be a count {countMax.empty() or count.exists()}tim-9:オフセットがある場合、c、cm、cd、cvではなく（c、cvではない）存在する必要があります。 / If there's an offset, there must be a when (and not C, CM, CD, CV) {offset.empty() or (when.exists() and ((when in ('C' | 'CM' | 'CD' | 'CV')).not()))}tim-10:時間がある場合、いつ、またはその逆もありません / If there's a timeOfDay, there cannot be a when, or vice versa {timeOfDay.empty() or when.empty()}</t>
   </si>
   <si>
     <t>Implies PIVL or EIVL</t>
@@ -439,7 +441,7 @@
     <t>回数に上限、下限の範囲がある場合は、このcountで示される回数が起きるまでは、エレメントは範囲の中にあると解釈されるべきである。</t>
   </si>
   <si>
-    <t>Repetitions may be limited by end time or total occurrences.</t>
+    <t>繰り返しは、終了時間または合計発生によって制限される場合があります。 / Repetitions may be limited by end time or total occurrences.</t>
   </si>
   <si>
     <t>PIVL.count</t>
@@ -495,7 +497,7 @@
 </t>
   </si>
   <si>
-    <t>s | min | h | d | wk | mo | a - unit of time (UCUM)</t>
+    <t>s |min |h |d |wk |mo |A-時間単位（ucum） / s | min | h | d | wk | mo | a - unit of time (UCUM)</t>
   </si>
   <si>
     <t>UCUM単位で表される継続時間についての単位。</t>
@@ -525,7 +527,7 @@
     <t>32ビットの数値。もし、値がそれを上回るようであればdecimalを使用する。</t>
   </si>
   <si>
-    <t>If no frequency is stated, the assumption is that the event occurs once per period, but systems SHOULD always be specific about this</t>
+    <t>頻度が記載されていない場合、イベントは期間ごとに1回発生するという仮定ですが、システムは常にこれについて具体的でなければなりません / If no frequency is stated, the assumption is that the event occurs once per period, but systems SHOULD always be specific about this</t>
   </si>
   <si>
     <t>Timing.repeat.frequencyMax</t>
@@ -570,7 +572,7 @@
     <t>Timing.repeat.dayOfWeek</t>
   </si>
   <si>
-    <t>mon | tue | wed | thu | fri | sat | sun</t>
+    <t>月|火|水|木|金|土|太陽 / mon | tue | wed | thu | fri | sat | sun</t>
   </si>
   <si>
     <t>期間として1週間以上が指定されていれば、指定された曜日のみで投与が行われる。</t>
@@ -642,7 +644,7 @@
 </t>
   </si>
   <si>
-    <t>BID | TID | QID | AM | PM | QD | QOD | +</t>
+    <t>入札|TID |QID |AM |PM |QD |qod |+ / BID | TID | QID | AM | PM | QD | QOD | +</t>
   </si>
   <si>
     <t>スケジュール上のタイミングを表すコード（あるいはcode.text内のテキスト）。BID(1日2回)のようなコードはどこにでもあるが、多くの医療機関は付加的なコードを定義している。もし、コードが示されていれば、構造化されたタイミングで完全に示されたデータであると解釈され、コードまたはTimingを解釈するためのデータであると解釈される。しかし、例外的に.repeat.bounds（コードは含まれない)はコードを上書きして適用される。</t>
